--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.53796514651603</v>
+        <v>7.237419336308855</v>
       </c>
       <c r="D2" t="n">
-        <v>44.30104563404365</v>
+        <v>7.198919915532093</v>
       </c>
       <c r="E2" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F2" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.9293013328383</v>
+        <v>1.938511466586224</v>
       </c>
       <c r="D3" t="n">
-        <v>11.94984786988434</v>
+        <v>1.941850278856205</v>
       </c>
       <c r="E3" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F3" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.50691470344527</v>
+        <v>1.707373639309856</v>
       </c>
       <c r="D4" t="n">
-        <v>10.75943593388599</v>
+        <v>1.748408339256474</v>
       </c>
       <c r="E4" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F4" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.13368760494071</v>
+        <v>3.434224235802866</v>
       </c>
       <c r="D5" t="n">
-        <v>21.42569219360335</v>
+        <v>3.481674981460544</v>
       </c>
       <c r="E5" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F5" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.33196443978348</v>
+        <v>4.928944221464816</v>
       </c>
       <c r="D6" t="n">
-        <v>31.45238081640993</v>
+        <v>5.111011882666614</v>
       </c>
       <c r="E6" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F6" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.22511472802676</v>
+        <v>5.074081143304348</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81342752833655</v>
+        <v>5.33218197335469</v>
       </c>
       <c r="E7" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F7" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.96038580513969</v>
+        <v>6.006062693335199</v>
       </c>
       <c r="D8" t="n">
-        <v>37.23595066348313</v>
+        <v>6.050841982816009</v>
       </c>
       <c r="E8" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F8" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.142057766355651</v>
+        <v>0.9980843870327933</v>
       </c>
       <c r="D9" t="n">
-        <v>6.615764857322458</v>
+        <v>1.075061789314899</v>
       </c>
       <c r="E9" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F9" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.57266977830715</v>
+        <v>2.205558838974911</v>
       </c>
       <c r="D10" t="n">
-        <v>11.68897631434645</v>
+        <v>1.899458651081298</v>
       </c>
       <c r="E10" t="n">
-        <v>12.62855486115645</v>
+        <v>2.052140164937923</v>
       </c>
       <c r="F10" t="n">
-        <v>12.88741647895632</v>
+        <v>2.094205177830402</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
